--- a/output/graficos_nacionales/plot_nacional_regiones_o_ocup_a_2020.xlsx
+++ b/output/graficos_nacionales/plot_nacional_regiones_o_ocup_a_2020.xlsx
@@ -78,7 +78,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-08-20 19:30</t>
+    <t xml:space="preserve">2026-08-20 21:36</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_nacionales/plot_nacional_regiones_o_ocup_a_2020.xlsx
+++ b/output/graficos_nacionales/plot_nacional_regiones_o_ocup_a_2020.xlsx
@@ -78,7 +78,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-08-20 21:36</t>
+    <t xml:space="preserve">2026-08-21 12:39</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_nacionales/plot_nacional_regiones_o_ocup_a_2020.xlsx
+++ b/output/graficos_nacionales/plot_nacional_regiones_o_ocup_a_2020.xlsx
@@ -78,7 +78,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-08-21 12:39</t>
+    <t xml:space="preserve">2026-09-07 12:20</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
